--- a/resources/Part_3_Statistics/S18_L116/3.15.Confidence-intervals.Two-means.Independent-samples-Part-2-exercise.xlsx
+++ b/resources/Part_3_Statistics/S18_L116/3.15.Confidence-intervals.Two-means.Independent-samples-Part-2-exercise.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18229"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="CI, indep, var unkwn" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>LA apples</t>
   </si>
@@ -49,6 +49,54 @@
   </si>
   <si>
     <t>Compare the result with the 95% confidence interval from the lesson</t>
+  </si>
+  <si>
+    <t>Task 1:</t>
+  </si>
+  <si>
+    <t>nx=</t>
+  </si>
+  <si>
+    <t>ny=</t>
+  </si>
+  <si>
+    <t>meanx=</t>
+  </si>
+  <si>
+    <t>meanY=</t>
+  </si>
+  <si>
+    <t>stdevX=</t>
+  </si>
+  <si>
+    <t>stdevY=</t>
+  </si>
+  <si>
+    <t>StdevP=</t>
+  </si>
+  <si>
+    <t>Confidence interval</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>alpha 10%</t>
+  </si>
+  <si>
+    <t>alpha/2=</t>
+  </si>
+  <si>
+    <t>t=</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 2: </t>
+  </si>
+  <si>
+    <t>Having a lower confidence (90% compared to 95%) allows a narrower interval ([0,51-0,88] compared to [0,47-0,92])</t>
   </si>
 </sst>
 </file>
@@ -56,7 +104,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -137,9 +185,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -147,19 +195,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -438,34 +487,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:N19"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:Q19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="1"/>
+    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85546875" style="1"/>
+    <col min="10" max="10" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
@@ -473,7 +523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -481,7 +531,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
@@ -489,46 +539,99 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
     </row>
-    <row r="9" spans="2:14" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="10"/>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="9">
+        <f>COUNT(B10:B19)</f>
+        <v>10</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="13">
+        <f>AVERAGE(B10:B19)</f>
+        <v>3.9409999999999998</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="10">
+        <f>_xlfn.STDEV.S(B10:B19)</f>
+        <v>0.18393537512458616</v>
+      </c>
       <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="L9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="10">
+        <f>(((F9-1)*(J9^2)+(F10-1)*(J10^2))/(F9+F10-2))^(1/2)</f>
+        <v>0.22456764014434494</v>
+      </c>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B10" s="5">
         <v>3.8</v>
       </c>
       <c r="C10" s="5">
         <v>3.02</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
+      <c r="E10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="9">
+        <f>COUNT(C10:C17)</f>
+        <v>8</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="13">
+        <f>AVERAGE(C10:C17)</f>
+        <v>3.2450000000000001</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="10">
+        <f>_xlfn.STDEV.S(C10:C17)</f>
+        <v>0.26790190102242384</v>
+      </c>
       <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-    </row>
-    <row r="11" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+      <c r="L10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>1.746</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>3.76</v>
       </c>
@@ -546,25 +649,37 @@
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>3.87</v>
       </c>
       <c r="C12" s="5">
         <v>3.24</v>
       </c>
-      <c r="E12" s="11"/>
+      <c r="E12" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="8"/>
+      <c r="G12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="10">
+        <f>(H9-H10)+Q10*SQRT((M9^2/F9)+(M9^2/F10))</f>
+        <v>0.88198703616263796</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="8">
+        <f>(H9-H10)-Q10*SQRT((M9^2/F9)+(M9^2/F10))</f>
+        <v>0.5100129638373615</v>
+      </c>
       <c r="K12" s="8"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>3.99</v>
       </c>
@@ -582,7 +697,7 @@
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B14" s="5">
         <v>4.0199999999999996</v>
       </c>
@@ -600,14 +715,19 @@
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>4.25</v>
       </c>
       <c r="C15" s="5">
         <v>3.15</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="F15" s="12"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -618,7 +738,7 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>4.13</v>
       </c>
@@ -636,7 +756,7 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>3.98</v>
       </c>
